--- a/tables/REGISTRY.xlsx
+++ b/tables/REGISTRY.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>한 행 = 시트 하나. Parent·ParentKey는 이 시트 행이 매달리는 상위 시트와 그 열, Uses는 라이브러리처럼 참조하는 시트. Active = N이면 그 시트를 읽지 않는다.</t>
+          <t>한 행 = 시트 하나. Parent·ParentKey는 이 시트 행이 매달리는 상위 시트와 그 열, Uses는 라이브러리처럼 참조하는 시트. File은 저장소 tables/의 xlsx 파일 이름(확장자 제외). 대부분 파일 1개 = 시트 1개이고, PlayerState·EliteState·BossState는 UnitState.xlsx 하나에 시트로 나뉠어 들어감. Active = N이면 그 시트를 읽지 않는다.</t>
         </is>
       </c>
     </row>
@@ -546,6 +546,11 @@
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>File</t>
         </is>
       </c>
     </row>
@@ -596,6 +601,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRY</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -644,6 +654,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -692,6 +707,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -740,6 +760,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>UnitStat</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -788,6 +813,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -836,6 +866,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -884,6 +919,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -932,6 +972,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -980,6 +1025,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -987,12 +1037,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>보스 페이즈</t>
+          <t>보스 상태</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>BossState</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1026,6 +1076,11 @@
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>UnitState</t>
         </is>
       </c>
     </row>
@@ -1076,6 +1131,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1122,6 +1182,117 @@
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>StageLayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>11013</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>플레이어 상태</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>PlayerState</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>UnitStat</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12001~</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>UnitState</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>11014</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>엘리트 상태</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EliteState</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>UnitStat</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13001~</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>UnitState</t>
         </is>
       </c>
     </row>

--- a/tables/REGISTRY.xlsx
+++ b/tables/REGISTRY.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>한 행 = 시트 하나. Parent·ParentKey는 이 시트 행이 매달리는 상위 시트와 그 열, Uses는 라이브러리처럼 참조하는 시트. File은 저장소 tables/의 xlsx 파일 이름(확장자 제외). 대부분 파일 1개 = 시트 1개이고, PlayerState·EliteState·BossState는 UnitState.xlsx 하나에 시트로 나뉠어 들어감. Active = N이면 그 시트를 읽지 않는다.</t>
+          <t>한 행 = 시트 하나. Parent·ParentKey는 이 시트 행이 매달리는 상위 시트와 그 열, Uses는 라이브러리처럼 참조하는 시트. File은 저장소 tables/의 xlsx 파일 이름(확장자 제외). 대부분 파일 1개 = 시트 1개이고, PlayerState·EliteState·BossState는 UnitState.xlsx, Weapon·Armor·Consumable은 Item.xlsx 하나에 시트로 나뉠어 들어감. Active = N이면 그 시트를 읽지 않는다.</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Item</t>
         </is>
       </c>
     </row>
@@ -1293,6 +1293,112 @@
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>UnitState</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>11015</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>방어구</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>14001~</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>11016</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>소모품</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>String, PlayerState</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15001~</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
         </is>
       </c>
     </row>

--- a/tables/REGISTRY.xlsx
+++ b/tables/REGISTRY.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>한 행 = 시트 하나. Parent·ParentKey는 이 시트 행이 매달리는 상위 시트와 그 열, Uses는 라이브러리처럼 참조하는 시트. File은 저장소 tables/의 xlsx 파일 이름(확장자 제외). 대부분 파일 1개 = 시트 1개이고, PlayerState·EliteState·BossState는 UnitState.xlsx, Weapon·Armor·Consumable은 Item.xlsx 하나에 시트로 나뉠어 들어감. Active = N이면 그 시트를 읽지 않는다.</t>
+          <t>한 행 = 시트 하나. Parent·ParentKey는 이 시트 행이 매달리는 상위 시트와 그 열, Uses는 라이브러리처럼 참조하는 시트. File은 저장소 tables/의 xlsx 파일 이름(확장자 제외). 대부분 파일 1개 = 시트 1개이고, PlayerState·EliteState·BossState는 UnitState.xlsx 하나에 시트로 나뉠어 들어감. 아이템은 Item 시트 하나(무기·방어구·소모품, ItemType으로 구분). Active = N이면 그 시트를 읽지 않는다.</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>무기</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Attack, Skill, String</t>
+          <t>Attack|Skill|String</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1293,112 +1293,6 @@
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>UnitState</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>11015</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>방어구</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>14001~</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>11016</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>소모품</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>String, PlayerState</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15001~</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
         </is>
       </c>
     </row>

--- a/tables/REGISTRY.xlsx
+++ b/tables/REGISTRY.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>시트 목록, 계층, ID 구간, 읽는 순서.</t>
+          <t>CSV,시트 목록, 계층, ID 구간, 읽는 순서.</t>
         </is>
       </c>
     </row>

--- a/tables/REGISTRY.xlsx
+++ b/tables/REGISTRY.xlsx
@@ -768,26 +768,26 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>11005</v>
+        <v>11006</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>공격</t>
+          <t>스킬</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>UnitStat</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>OwnerID</t>
+          <t>WeaponID</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -797,11 +797,11 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5001~</t>
+          <t>7001~</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -815,42 +815,42 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>11006</v>
+        <v>11007</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>스킬</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>WeaponID</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Attack, String</t>
+          <t>Skill|String</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7001~</t>
+          <t>6001~</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -868,46 +868,46 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Item</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>11007</v>
+        <v>11008</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>플레이어</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>UnitStat</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Attack|Skill|String</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6001~</t>
+          <t>2001~</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -921,22 +921,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Player</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>11008</v>
+        <v>11009</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>플레이어</t>
+          <t>몬스터</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Monster</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2001~</t>
+          <t>3001~</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -974,22 +974,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Monster</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>11009</v>
+        <v>11010</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>몬스터</t>
+          <t>보스 상태</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>BossState</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3001~</t>
+          <t>4001~</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -1027,46 +1027,46 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>UnitState</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>11010</v>
+        <v>11011</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>보스 상태</t>
+          <t>스테이지</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BossState</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>UnitStat</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>UnitID</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>String, Monster(스폰 JSON)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4001~</t>
+          <t>8001~</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1080,46 +1080,46 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>UnitState</t>
+          <t>Stage</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>11011</v>
+        <v>11012</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>스테이지</t>
+          <t>배경 레이어</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>StageLayer</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>StageID</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>String, Monster(스폰 JSON)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8001~</t>
+          <t>9001~</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1133,50 +1133,50 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>StageLayer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>11012</v>
+        <v>11013</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>배경 레이어</t>
+          <t>플레이어 상태</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>StageLayer</t>
+          <t>PlayerState</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>UnitStat</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>StageID</t>
+          <t>UnitID</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>State</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9001~</t>
+          <t>12001~</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>StageLayer</t>
+          <t>UnitState</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>11013</v>
+        <v>11014</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>플레이어 상태</t>
+          <t>엘리트 상태</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PlayerState</t>
+          <t>EliteState</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12001~</t>
+          <t>13001~</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1244,57 +1244,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>11014</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>엘리트 상태</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>EliteState</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>UnitStat</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>UnitID</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13001~</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>UnitState</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/REGISTRY.xlsx
+++ b/tables/REGISTRY.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>State, String</t>
+          <t>State, Language</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Skill|String</t>
+          <t>Skill|Language</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>String, Monster(스폰 JSON)</t>
+          <t>Language, Monster(스폰 JSON)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
